--- a/data/trans_orig/P04D$aparatos-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04D$aparatos-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>157087</t>
+          <t>158974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193536</t>
+          <t>191821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139590</t>
+          <t>140998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>175422</t>
+          <t>178018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>308029</t>
+          <t>307003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>356586</t>
+          <t>359234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18622</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83545</t>
+          <t>84126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56825</t>
+          <t>56190</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86644</t>
+          <t>84985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118681</t>
+          <t>120349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161211</t>
+          <t>162014</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31253</t>
+          <t>31321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>42324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69491</t>
+          <t>68962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79657</t>
+          <t>78871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117273</t>
+          <t>117019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>319091</t>
+          <t>319544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363087</t>
+          <t>364326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340265</t>
+          <t>341075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>383015</t>
+          <t>384675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>676693</t>
+          <t>674784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736734</t>
+          <t>738265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23665</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>23055</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42638</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87746</t>
+          <t>87234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126299</t>
+          <t>125348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82898</t>
+          <t>81791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118755</t>
+          <t>119732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178981</t>
+          <t>180229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231672</t>
+          <t>233282</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56143</t>
+          <t>57006</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>61937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104346</t>
+          <t>106207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>228099</t>
+          <t>227667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>258865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>252747</t>
+          <t>254130</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>284296</t>
+          <t>283936</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>491635</t>
+          <t>492614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>534679</t>
+          <t>534438</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57887</t>
+          <t>56929</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87325</t>
+          <t>87756</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50294</t>
+          <t>50593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>79633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117376</t>
+          <t>115037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156671</t>
+          <t>156430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198883</t>
+          <t>199068</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>238684</t>
+          <t>238668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>222384</t>
+          <t>221733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>261954</t>
+          <t>261249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>433656</t>
+          <t>430057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>490781</t>
+          <t>485549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31749</t>
+          <t>32867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24895</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102948</t>
+          <t>104179</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>142177</t>
+          <t>141001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>104947</t>
+          <t>104335</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>142201</t>
+          <t>141779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>219092</t>
+          <t>219880</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>271842</t>
+          <t>272438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20472</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116285</t>
+          <t>115527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146310</t>
+          <t>145808</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102556</t>
+          <t>100521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131373</t>
+          <t>131141</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>225840</t>
+          <t>226520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>268938</t>
+          <t>269853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38693</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>39117</t>
+          <t>39969</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>66181</t>
+          <t>67440</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>60115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>52234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78595</t>
+          <t>79758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>92009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129525</t>
+          <t>129927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>20490</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>172307</t>
+          <t>171632</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>204289</t>
+          <t>203756</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>184373</t>
+          <t>184587</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>214272</t>
+          <t>214083</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>366304</t>
+          <t>366308</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>412832</t>
+          <t>411176</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22255</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33151</t>
+          <t>33106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55893</t>
+          <t>56411</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>85963</t>
+          <t>86740</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84481</t>
+          <t>83230</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115793</t>
+          <t>119022</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159005</t>
+          <t>160918</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>458600</t>
+          <t>457031</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>506731</t>
+          <t>507543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>477719</t>
+          <t>477935</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>527560</t>
+          <t>526223</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>950780</t>
+          <t>952588</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1021522</t>
+          <t>1020422</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142604</t>
+          <t>141553</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>188693</t>
+          <t>188561</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147463</t>
+          <t>147009</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>196617</t>
+          <t>192600</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>300447</t>
+          <t>298754</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>365431</t>
+          <t>365700</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3822,82 +3822,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>17354</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>27060</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>29038</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>19185</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>41516</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
           <t>3,06%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>17354</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>10577</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>28512</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>29038</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>18072</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>40457</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>347319</t>
+          <t>350815</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>405328</t>
+          <t>409872</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>429334</t>
+          <t>430393</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>490184</t>
+          <t>490596</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>798459</t>
+          <t>797946</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>881879</t>
+          <t>881114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>25801</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>32153</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>51950</t>
+          <t>50133</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>342973</t>
+          <t>338309</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>400585</t>
+          <t>395743</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>317391</t>
+          <t>320141</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>375900</t>
+          <t>378935</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>672966</t>
+          <t>673202</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>755799</t>
+          <t>755816</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14498</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>32985</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>52790</t>
+          <t>50897</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2104605</t>
+          <t>2104221</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2219363</t>
+          <t>2220822</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2250375</t>
+          <t>2252736</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2369772</t>
+          <t>2368984</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4390928</t>
+          <t>4389541</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4557754</t>
+          <t>4560390</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>87160</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>130727</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>76214</t>
+          <t>76675</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>118292</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>174013</t>
+          <t>177222</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>232053</t>
+          <t>234637</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>967788</t>
+          <t>961210</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1074169</t>
+          <t>1074530</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,39 +4621,39 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>28,11%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>31,42%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1005887</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>953120</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>1056955</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
           <t>28,3%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>1005887</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>953284</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>1065229</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
           <t>26,82%</t>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1946023</t>
+          <t>1944460</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2104058</t>
+          <t>2096331</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>117068</t>
+          <t>117374</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>167283</t>
+          <t>166824</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>133591</t>
+          <t>135924</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>184342</t>
+          <t>184531</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>269870</t>
+          <t>266958</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>337742</t>
+          <t>339684</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32766</t>
+          <t>33104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58156</t>
+          <t>58490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55913</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>69953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105548</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -5185,82 +5185,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4496</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>898</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4300</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86419</t>
+          <t>85192</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121542</t>
+          <t>118287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101947</t>
+          <t>100982</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136131</t>
+          <t>133357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>195127</t>
+          <t>198063</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>245003</t>
+          <t>243388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125834</t>
+          <t>127434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164036</t>
+          <t>162962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>110902</t>
+          <t>112301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144513</t>
+          <t>145899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249999</t>
+          <t>250892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>299368</t>
+          <t>299411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155784</t>
+          <t>156838</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199673</t>
+          <t>200812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>148495</t>
+          <t>149118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192648</t>
+          <t>193230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>317641</t>
+          <t>320973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>380382</t>
+          <t>382487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165961</t>
+          <t>165802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211492</t>
+          <t>208709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203320</t>
+          <t>203822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>250169</t>
+          <t>251258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>382901</t>
+          <t>381634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>447841</t>
+          <t>447470</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>116879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158070</t>
+          <t>156324</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>100627</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140486</t>
+          <t>139940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228066</t>
+          <t>229487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285966</t>
+          <t>284834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>242146</t>
+          <t>241593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>269607</t>
+          <t>269080</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257077</t>
+          <t>256789</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>286021</t>
+          <t>284956</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>509865</t>
+          <t>506824</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>548258</t>
+          <t>547371</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36722</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63112</t>
+          <t>62297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>41604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67741</t>
+          <t>68575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84794</t>
+          <t>85809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121691</t>
+          <t>122717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>210648</t>
+          <t>209111</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>247077</t>
+          <t>247023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223086</t>
+          <t>223235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>262603</t>
+          <t>264254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>444863</t>
+          <t>441469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>501430</t>
+          <t>498646</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31243</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51218</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92086</t>
+          <t>91167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>128023</t>
+          <t>127696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88338</t>
+          <t>85372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125012</t>
+          <t>124733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>191788</t>
+          <t>191076</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>243199</t>
+          <t>243834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24196</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24107</t>
+          <t>23782</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47176</t>
+          <t>49334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178673</t>
+          <t>179520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196962</t>
+          <t>196838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185790</t>
+          <t>185909</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202812</t>
+          <t>202919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>371239</t>
+          <t>369510</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396012</t>
+          <t>394572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -7009,97 +7009,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>851</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>5490</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>5109</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>27759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50652</t>
+          <t>50541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -7235,12 +7235,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7320,12 +7320,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>53426</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>82166</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52265</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80772</t>
+          <t>79207</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111769</t>
+          <t>112543</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>150955</t>
+          <t>152575</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27046</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51232</t>
+          <t>50759</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38622</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51938</t>
+          <t>52371</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82812</t>
+          <t>83192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>53043</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82320</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70827</t>
+          <t>71992</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>100910</t>
+          <t>103970</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132894</t>
+          <t>132615</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174531</t>
+          <t>175082</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>76123</t>
+          <t>77758</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107524</t>
+          <t>108592</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>79025</t>
+          <t>78791</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>111497</t>
+          <t>109750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>163988</t>
+          <t>162893</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>207409</t>
+          <t>209508</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>309800</t>
+          <t>306477</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>363914</t>
+          <t>364795</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>328768</t>
+          <t>327175</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>381516</t>
+          <t>382029</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>651541</t>
+          <t>651996</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>730389</t>
+          <t>728982</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>35670</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59614</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142486</t>
+          <t>141355</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>189455</t>
+          <t>188576</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>157504</t>
+          <t>157106</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>206810</t>
+          <t>206716</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>311404</t>
+          <t>314418</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>378398</t>
+          <t>380380</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8147,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>110782</t>
+          <t>110703</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>152325</t>
+          <t>155464</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>116336</t>
+          <t>115490</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>159569</t>
+          <t>161868</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>240423</t>
+          <t>240568</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>304923</t>
+          <t>300333</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>471188</t>
+          <t>472859</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>528649</t>
+          <t>526752</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>480467</t>
+          <t>479987</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>538208</t>
+          <t>537493</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>973207</t>
+          <t>971663</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1050687</t>
+          <t>1051716</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,54%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>242997</t>
+          <t>241646</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>298091</t>
+          <t>297947</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>275592</t>
+          <t>276386</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>331471</t>
+          <t>335381</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>535126</t>
+          <t>532999</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>609785</t>
+          <t>612624</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,18%</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>16990</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>23084</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1737791</t>
+          <t>1741456</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1856233</t>
+          <t>1860158</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1797706</t>
+          <t>1789234</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1912004</t>
+          <t>1913164</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3570685</t>
+          <t>3571319</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3733500</t>
+          <t>3737823</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,87%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>76959</t>
+          <t>76700</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>115788</t>
+          <t>116207</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>70912</t>
+          <t>70305</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>107083</t>
+          <t>107476</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>157173</t>
+          <t>156731</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>211025</t>
+          <t>211574</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>913455</t>
+          <t>917657</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1025358</t>
+          <t>1024029</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1037651</t>
+          <t>1035693</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1155967</t>
+          <t>1148130</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1982149</t>
+          <t>1986461</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2144756</t>
+          <t>2142806</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>488903</t>
+          <t>492038</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>580562</t>
+          <t>577072</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>473334</t>
+          <t>476803</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>561205</t>
+          <t>562513</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>984256</t>
+          <t>986040</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1108322</t>
+          <t>1118529</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de calefacción que tiene en su vivienda (multirrespuesta) en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>110361</t>
+          <t>111680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153063</t>
+          <t>155115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122851</t>
+          <t>123353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152435</t>
+          <t>151700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244605</t>
+          <t>244462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>295905</t>
+          <t>295536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32792</t>
+          <t>31850</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92725</t>
+          <t>93395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>133953</t>
+          <t>133729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81513</t>
+          <t>80539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107095</t>
+          <t>105781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>183229</t>
+          <t>182308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>233389</t>
+          <t>229950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -9751,12 +9751,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41760</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77618</t>
+          <t>77547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69672</t>
+          <t>67128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92007</t>
+          <t>90161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134939</t>
+          <t>133184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410781</t>
+          <t>411588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>454439</t>
+          <t>453364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>421863</t>
+          <t>422922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450096</t>
+          <t>450185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>841426</t>
+          <t>846888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>895814</t>
+          <t>896981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25647</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9734</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31917</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>27647</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>44512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -10207,12 +10207,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40595</t>
+          <t>40053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78546</t>
+          <t>75469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>45714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70082</t>
+          <t>69841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93685</t>
+          <t>94371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138316</t>
+          <t>137696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210570</t>
+          <t>210731</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242963</t>
+          <t>242573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241339</t>
+          <t>240878</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>269602</t>
+          <t>269919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>460334</t>
+          <t>458962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>502824</t>
+          <t>503398</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38988</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>31358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>52721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55828</t>
+          <t>54920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85500</t>
+          <t>84503</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36825</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62909</t>
+          <t>62261</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>34336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55706</t>
+          <t>56895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77917</t>
+          <t>77696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111780</t>
+          <t>111270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -10663,12 +10663,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>28980</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>100450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>139636</t>
+          <t>143024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136457</t>
+          <t>130989</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>263375</t>
+          <t>265658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241499</t>
+          <t>245310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388039</t>
+          <t>386007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>48523</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92563</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124462</t>
+          <t>125778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170958</t>
+          <t>171057</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84496</t>
+          <t>86568</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>176221</t>
+          <t>177761</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>205045</t>
+          <t>196572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331858</t>
+          <t>328790</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -11119,12 +11119,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18503</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247989</t>
+          <t>237807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>30328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300054</t>
+          <t>287698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -11236,12 +11236,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173030</t>
+          <t>173899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178352</t>
+          <t>178417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11271,12 +11271,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>246321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>255377</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11286,12 +11286,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>422890</t>
+          <t>421559</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>432498</t>
+          <t>432380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11321,12 +11321,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -11349,97 +11349,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>413</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2533</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -11575,12 +11575,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>508</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>131521</t>
+          <t>131748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161576</t>
+          <t>161225</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>124570</t>
+          <t>124588</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150678</t>
+          <t>150808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>265283</t>
+          <t>263155</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>303455</t>
+          <t>303499</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61923</t>
+          <t>62417</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90480</t>
+          <t>91705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66861</t>
+          <t>66690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>91372</t>
+          <t>93187</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137712</t>
+          <t>138089</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>174298</t>
+          <t>174904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32268</t>
+          <t>31575</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>54329</t>
+          <t>52742</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>62987</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>91970</t>
+          <t>91747</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -12031,12 +12031,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12066,12 +12066,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -12101,12 +12101,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12116,12 +12116,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>169809</t>
+          <t>173336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>231242</t>
+          <t>231582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>245911</t>
+          <t>246923</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>658879</t>
+          <t>663215</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>443529</t>
+          <t>439637</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>870905</t>
+          <t>926467</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>25197</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49685</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>56570</t>
+          <t>55891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95683</t>
+          <t>97521</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>155805</t>
+          <t>156823</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>211303</t>
+          <t>207645</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76636</t>
+          <t>84138</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>265001</t>
+          <t>264730</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>250086</t>
+          <t>225540</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>449813</t>
+          <t>450617</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>174152</t>
+          <t>174960</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>230515</t>
+          <t>229223</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>92110</t>
+          <t>84872</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>291900</t>
+          <t>292670</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12537,12 +12537,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12557,12 +12557,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>278006</t>
+          <t>262088</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>500141</t>
+          <t>501154</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12572,12 +12572,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>278776</t>
+          <t>298153</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>849246</t>
+          <t>850559</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>636601</t>
+          <t>636660</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>662030</t>
+          <t>662432</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>786911</t>
+          <t>714892</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1500634</t>
+          <t>1499259</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>23761</t>
+          <t>23714</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>47451</t>
+          <t>47736</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>636025</t>
+          <t>617419</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>31076</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>51476</t>
+          <t>52681</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>88286</t>
+          <t>87687</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>828988</t>
+          <t>896633</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -12943,12 +12943,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>29512</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12978,12 +12978,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>19469</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>47225</t>
+          <t>47893</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1562695</t>
+          <t>1609846</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2236086</t>
+          <t>2234310</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2330217</t>
+          <t>2339580</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2672409</t>
+          <t>2679549</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4041784</t>
+          <t>3973335</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4782236</t>
+          <t>4786039</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>157265</t>
+          <t>156025</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>238211</t>
+          <t>240011</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>176683</t>
+          <t>175549</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>247518</t>
+          <t>242422</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>359613</t>
+          <t>357292</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>465817</t>
+          <t>466268</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>615159</t>
+          <t>616833</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1480020</t>
+          <t>1457534</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>462986</t>
+          <t>462330</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>626384</t>
+          <t>621803</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1172093</t>
+          <t>1155383</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2185682</t>
+          <t>2117910</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -13399,12 +13399,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>276342</t>
+          <t>287278</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>413108</t>
+          <t>412953</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -13434,12 +13434,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>363645</t>
+          <t>358684</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>641776</t>
+          <t>652698</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13449,47 +13449,47 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>805297</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>703072</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>1014943</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
           <t>9,82%</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>981</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>805297</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>703057</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
-        <is>
-          <t>1011512</t>
-        </is>
-      </c>
-      <c r="U39" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
